--- a/data/trans_dic/P1428-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1428-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,22</t>
+          <t>4,57; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,96</t>
+          <t>4,2; 8,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,57</t>
+          <t>3,0; 6,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,56</t>
+          <t>4,05; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 22,17</t>
+          <t>16,21; 22,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,42</t>
+          <t>10,94; 16,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,66</t>
+          <t>9,79; 15,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,29</t>
+          <t>16,27; 20,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 14,49</t>
+          <t>11,0; 14,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,63</t>
+          <t>8,35; 11,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,77</t>
+          <t>6,83; 9,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 14,03</t>
+          <t>10,68; 13,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,58</t>
+          <t>5,93; 9,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,2</t>
+          <t>4,99; 8,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,67</t>
+          <t>2,37; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,96</t>
+          <t>3,43; 5,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,8</t>
+          <t>14,4; 19,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 14,48</t>
+          <t>10,25; 14,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 12,78</t>
+          <t>8,81; 12,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 15,1</t>
+          <t>11,85; 15,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,06</t>
+          <t>11,0; 14,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,71</t>
+          <t>8,05; 10,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,25</t>
+          <t>5,94; 8,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,46</t>
+          <t>7,95; 9,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,23</t>
+          <t>5,27; 9,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,14</t>
+          <t>2,36; 5,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,62</t>
+          <t>2,69; 5,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,01</t>
+          <t>3,69; 6,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 21,06</t>
+          <t>14,98; 21,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,31</t>
+          <t>8,63; 13,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,64</t>
+          <t>5,79; 9,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 64,29</t>
+          <t>9,16; 13,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,38</t>
+          <t>10,97; 14,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,81</t>
+          <t>5,93; 8,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,06</t>
+          <t>4,59; 7,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 47,08</t>
+          <t>6,89; 9,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,55</t>
+          <t>6,09; 9,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,22</t>
+          <t>3,38; 6,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,35</t>
+          <t>2,13; 4,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,84</t>
+          <t>4,8; 7,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,39</t>
+          <t>14,88; 19,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 15,0</t>
+          <t>10,83; 14,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,79</t>
+          <t>6,24; 9,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,12</t>
+          <t>13,72; 17,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 14,12</t>
+          <t>11,24; 14,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,24</t>
+          <t>7,55; 10,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,71</t>
+          <t>4,43; 6,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,24</t>
+          <t>9,9; 12,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,15</t>
+          <t>6,46; 8,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,99</t>
+          <t>4,41; 6,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,3</t>
+          <t>2,96; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,87</t>
+          <t>4,55; 5,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,97</t>
+          <t>16,39; 19,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,51</t>
+          <t>11,3; 13,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,45</t>
+          <t>8,41; 10,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 36,3</t>
+          <t>13,47; 15,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,68; 13,36</t>
+          <t>11,69; 13,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,57</t>
+          <t>8,2; 9,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,16</t>
+          <t>5,94; 7,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 24,01</t>
+          <t>9,31; 10,46</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>127700</t>
+          <t>134225</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>163744</t>
+          <t>172023</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31122; 57021</t>
+          <t>31683; 55940</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30314; 56026</t>
+          <t>29524; 57068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20261; 44313</t>
+          <t>20220; 41311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26898; 47977</t>
+          <t>27963; 51068</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>112315; 152596</t>
+          <t>111603; 152234</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74768; 114445</t>
+          <t>76283; 115169</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64440; 98652</t>
+          <t>65889; 102180</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114318; 143513</t>
+          <t>119023; 152449</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>152471; 200296</t>
+          <t>152031; 198980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114394; 162884</t>
+          <t>116969; 163495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92651; 131727</t>
+          <t>92013; 131629</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>145004; 183632</t>
+          <t>151735; 193680</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>47270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>127957</t>
+          <t>142319</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>170856</t>
+          <t>189589</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59458; 92169</t>
+          <t>57011; 89834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50698; 83462</t>
+          <t>50802; 82424</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24668; 47750</t>
+          <t>24211; 48165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20000; 59058</t>
+          <t>35943; 61484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>143611; 191709</t>
+          <t>139490; 190475</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104570; 148980</t>
+          <t>105458; 148836</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91880; 133239</t>
+          <t>91913; 133879</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112814; 143817</t>
+          <t>126086; 160635</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>209543; 271289</t>
+          <t>212408; 271449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164035; 219284</t>
+          <t>164798; 219050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122746; 170442</t>
+          <t>122589; 171595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>109090; 202702</t>
+          <t>167782; 210666</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>280044</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>317142</t>
+          <t>127854</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35292; 62657</t>
+          <t>35771; 62244</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17054; 38961</t>
+          <t>17869; 39993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20664; 42715</t>
+          <t>20437; 40797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27308; 49246</t>
+          <t>29565; 53765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103654; 144034</t>
+          <t>102440; 143666</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66299; 103418</t>
+          <t>67063; 103066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42316; 75711</t>
+          <t>45486; 76169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90607; 596230</t>
+          <t>73752; 104917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147491; 195909</t>
+          <t>149455; 194743</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90328; 135283</t>
+          <t>91033; 133605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70812; 109028</t>
+          <t>70847; 109352</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122027; 767576</t>
+          <t>110751; 147909</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>161489</t>
+          <t>170803</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>219013</t>
+          <t>230408</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58415; 89937</t>
+          <t>57381; 88682</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32948; 58967</t>
+          <t>32063; 60002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19090; 40758</t>
+          <t>19961; 42093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46193; 72420</t>
+          <t>47325; 73458</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151620; 201414</t>
+          <t>154557; 200755</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111758; 157815</t>
+          <t>113888; 157731</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62312; 102161</t>
+          <t>65131; 100447</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130073; 186880</t>
+          <t>153296; 193543</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223704; 279724</t>
+          <t>222563; 281671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152655; 204842</t>
+          <t>150945; 204398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89097; 132888</t>
+          <t>87733; 133004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>188643; 246663</t>
+          <t>208345; 255174</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>208868; 267097</t>
+          <t>211644; 267642</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151392; 205192</t>
+          <t>150975; 206819</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101492; 146115</t>
+          <t>100603; 145592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136351; 202713</t>
+          <t>160410; 210735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>552263; 640890</t>
+          <t>553969; 642144</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>398302; 480345</t>
+          <t>401719; 481574</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>296250; 370515</t>
+          <t>298270; 371859</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>508592; 1323440</t>
+          <t>500818; 566276</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>777516; 889127</t>
+          <t>778081; 889635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569815; 668340</t>
+          <t>572809; 671632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>408237; 496976</t>
+          <t>412329; 494081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>661515; 1704021</t>
+          <t>673935; 757593</t>
         </is>
       </c>
     </row>
